--- a/DQSYM/00_ComponentTest/00_Generator/DQGEN.xlsx
+++ b/DQSYM/00_ComponentTest/00_Generator/DQGEN.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB11D3B0-00AA-4796-A162-AB255C3B6903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F958EC3F-983D-4154-BD0C-0C33713144CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21710" yWindow="-11280" windowWidth="21820" windowHeight="37900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RLC" sheetId="7" r:id="rId1"/>
@@ -1759,7 +1759,7 @@
         <v>0.1</v>
       </c>
       <c r="E2" s="35">
-        <v>1</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="F2" s="42">
         <v>0</v>
@@ -1788,7 +1788,7 @@
         <v>0.1</v>
       </c>
       <c r="E3" s="35">
-        <v>1</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="F3" s="42">
         <v>0</v>
@@ -1820,7 +1820,7 @@
         <v>0.1</v>
       </c>
       <c r="E4" s="35">
-        <v>1</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="F4" s="42">
         <v>0</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="42">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="G5" s="35">
         <v>4</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="42">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="G6" s="35">
         <v>5</v>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="42">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="G7" s="35">
         <v>6</v>
